--- a/BKC01D.xlsx
+++ b/BKC01D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="233">
   <si>
     <t/>
   </si>
@@ -301,283 +301,271 @@
     <t>15</t>
   </si>
   <si>
-    <t>10040350</t>
-  </si>
-  <si>
-    <t>ESKULIN/K CLG PNK100</t>
+    <t>20132819</t>
+  </si>
+  <si>
+    <t>BLGIO PMDE BBLGUM 40</t>
+  </si>
+  <si>
+    <t>20115501</t>
+  </si>
+  <si>
+    <t>KODOMO P/G MIXBRY45</t>
+  </si>
+  <si>
+    <t>20091175</t>
+  </si>
+  <si>
+    <t>PEPSODNT KIDS STR 45</t>
+  </si>
+  <si>
+    <t>10004107</t>
+  </si>
+  <si>
+    <t>KODOMO P/G STRAWB.45</t>
+  </si>
+  <si>
+    <t>20011206</t>
+  </si>
+  <si>
+    <t>PIGEON BTOL RP-4 ECO</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20052754</t>
+  </si>
+  <si>
+    <t>PIGEON BTL STD 50ML</t>
+  </si>
+  <si>
+    <t>20132006</t>
+  </si>
+  <si>
+    <t>P/AVT BTLE PLN 125ML</t>
+  </si>
+  <si>
+    <t>20134490</t>
+  </si>
+  <si>
+    <t>P/AVT BTTLE GRAFE260</t>
+  </si>
+  <si>
+    <t>20091617</t>
+  </si>
+  <si>
+    <t>HUKI BTL PP SP RN240</t>
+  </si>
+  <si>
+    <t>20011207</t>
+  </si>
+  <si>
+    <t>PIGEON BTOL RP-8 ECO</t>
+  </si>
+  <si>
+    <t>20002133</t>
+  </si>
+  <si>
+    <t>IDM CT.BUD BABY R100</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20115786</t>
+  </si>
+  <si>
+    <t>IDM CTN.BUDS RFL 100</t>
+  </si>
+  <si>
+    <t>20098361</t>
+  </si>
+  <si>
+    <t>IDM CT.BUDS SPRL 100</t>
+  </si>
+  <si>
+    <t>20107245</t>
+  </si>
+  <si>
+    <t>PEPSODNT KDS PTRCK45</t>
+  </si>
+  <si>
+    <t>10000189</t>
+  </si>
+  <si>
+    <t>KODOMO PASTA+SKT ZIG</t>
+  </si>
+  <si>
+    <t>20037215</t>
+  </si>
+  <si>
+    <t>KODOMO PRO KIDS 1</t>
+  </si>
+  <si>
+    <t>RT,(E-0B)</t>
+  </si>
+  <si>
+    <t>20037216</t>
+  </si>
+  <si>
+    <t>KODOMO PRO KIDS 2</t>
+  </si>
+  <si>
+    <t>20135402</t>
+  </si>
+  <si>
+    <t>KODOMO TBRUSH FLEXY</t>
+  </si>
+  <si>
+    <t>10014741</t>
+  </si>
+  <si>
+    <t>FORMULA PG+SK BL ORG</t>
+  </si>
+  <si>
+    <t>10028140</t>
+  </si>
+  <si>
+    <t>FRMULA SG JNR EX.SFT</t>
+  </si>
+  <si>
+    <t>10014740</t>
+  </si>
+  <si>
+    <t>FORMULA PG+SK BL STR</t>
+  </si>
+  <si>
+    <t>10017886</t>
+  </si>
+  <si>
+    <t>ORAL B S/G MCKY SOFT</t>
+  </si>
+  <si>
+    <t>20044538</t>
+  </si>
+  <si>
+    <t>HUKI DOT SLC NPL.3/L</t>
+  </si>
+  <si>
+    <t>10019114</t>
+  </si>
+  <si>
+    <t>PIGEON SL.PACIFIER 2</t>
+  </si>
+  <si>
+    <t>20062263</t>
+  </si>
+  <si>
+    <t>PIGEON PRS NPL L 3'S</t>
+  </si>
+  <si>
+    <t>20128874</t>
+  </si>
+  <si>
+    <t>P/A TEAT F/F NRML 2S</t>
+  </si>
+  <si>
+    <t>10011772</t>
+  </si>
+  <si>
+    <t>CUSSONS B/CRM MILD50</t>
+  </si>
+  <si>
+    <t>10033930</t>
+  </si>
+  <si>
+    <t>CUSSON B/CRM SOFT50</t>
+  </si>
+  <si>
+    <t>20133137</t>
+  </si>
+  <si>
+    <t>MY BB FC&amp;BDY CRM 50G</t>
+  </si>
+  <si>
+    <t>20116527</t>
+  </si>
+  <si>
+    <t>ZWITSAL F&amp;B CREAM 50</t>
+  </si>
+  <si>
+    <t>PT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20135794</t>
+  </si>
+  <si>
+    <t>MY BB SOAP SWT.FLO75</t>
+  </si>
+  <si>
+    <t>20099248</t>
+  </si>
+  <si>
+    <t>LCTACYD BB.LIQ SP 60</t>
+  </si>
+  <si>
+    <t>20004868</t>
+  </si>
+  <si>
+    <t>JOHNSON LOTN REG 100</t>
+  </si>
+  <si>
+    <t>20053295</t>
+  </si>
+  <si>
+    <t>JHNSN COLG HPY/B 100</t>
+  </si>
+  <si>
+    <t>20071629</t>
+  </si>
+  <si>
+    <t>JHNSON COLG SLDE 100</t>
+  </si>
+  <si>
+    <t>20013772</t>
+  </si>
+  <si>
+    <t>JOHNSON COLG SUMR100</t>
+  </si>
+  <si>
+    <t>10038388</t>
+  </si>
+  <si>
+    <t>JOHNSON BABY OIL 50M</t>
+  </si>
+  <si>
+    <t>20133138</t>
+  </si>
+  <si>
+    <t>MY BABY BB/OIL PLS90</t>
+  </si>
+  <si>
+    <t>10028608</t>
+  </si>
+  <si>
+    <t>CUSSONS B/OIL SFT100</t>
+  </si>
+  <si>
+    <t>20035884</t>
+  </si>
+  <si>
+    <t>CUSSONS HL.NAT KM100</t>
+  </si>
+  <si>
+    <t>20009870</t>
+  </si>
+  <si>
+    <t>ZWITSAL SHP NAT 100</t>
+  </si>
+  <si>
+    <t>20123404</t>
+  </si>
+  <si>
+    <t>ZWTSAL BB ANBACT 200</t>
   </si>
   <si>
     <t>16</t>
-  </si>
-  <si>
-    <t>20132819</t>
-  </si>
-  <si>
-    <t>BLGIO PMDE BBLGUM 40</t>
-  </si>
-  <si>
-    <t>20115501</t>
-  </si>
-  <si>
-    <t>KODOMO P/G MIXBRY45</t>
-  </si>
-  <si>
-    <t>20091175</t>
-  </si>
-  <si>
-    <t>PEPSODNT KIDS STR 45</t>
-  </si>
-  <si>
-    <t>10004107</t>
-  </si>
-  <si>
-    <t>KODOMO P/G STRAWB.45</t>
-  </si>
-  <si>
-    <t>20011206</t>
-  </si>
-  <si>
-    <t>PIGEON BTOL RP-4 ECO</t>
-  </si>
-  <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>20128809</t>
-  </si>
-  <si>
-    <t>P/AVT BTTLE CLSC 260</t>
-  </si>
-  <si>
-    <t>20052754</t>
-  </si>
-  <si>
-    <t>PIGEON BTL STD 50ML</t>
-  </si>
-  <si>
-    <t>20132006</t>
-  </si>
-  <si>
-    <t>P/AVT BTLE PLN 125ML</t>
-  </si>
-  <si>
-    <t>20134490</t>
-  </si>
-  <si>
-    <t>P/AVT BTTLE GRAFE260</t>
-  </si>
-  <si>
-    <t>20091617</t>
-  </si>
-  <si>
-    <t>HUKI BTL PP SP RN240</t>
-  </si>
-  <si>
-    <t>20011207</t>
-  </si>
-  <si>
-    <t>PIGEON BTOL RP-8 ECO</t>
-  </si>
-  <si>
-    <t>20002133</t>
-  </si>
-  <si>
-    <t>IDM CT.BUD BABY R100</t>
-  </si>
-  <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20115786</t>
-  </si>
-  <si>
-    <t>IDM CTN.BUDS RFL 100</t>
-  </si>
-  <si>
-    <t>20098361</t>
-  </si>
-  <si>
-    <t>IDM CT.BUDS SPRL 100</t>
-  </si>
-  <si>
-    <t>20107245</t>
-  </si>
-  <si>
-    <t>PEPSODNT KDS PTRCK45</t>
-  </si>
-  <si>
-    <t>10000189</t>
-  </si>
-  <si>
-    <t>KODOMO PASTA+SKT ZIG</t>
-  </si>
-  <si>
-    <t>20037215</t>
-  </si>
-  <si>
-    <t>KODOMO PRO KIDS 1</t>
-  </si>
-  <si>
-    <t>RT,(E-0B)</t>
-  </si>
-  <si>
-    <t>20037216</t>
-  </si>
-  <si>
-    <t>KODOMO PRO KIDS 2</t>
-  </si>
-  <si>
-    <t>20135402</t>
-  </si>
-  <si>
-    <t>KODOMO TBRUSH FLEXY</t>
-  </si>
-  <si>
-    <t>10014741</t>
-  </si>
-  <si>
-    <t>FORMULA PG+SK BL ORG</t>
-  </si>
-  <si>
-    <t>10028140</t>
-  </si>
-  <si>
-    <t>FRMULA SG JNR EX.SFT</t>
-  </si>
-  <si>
-    <t>10014740</t>
-  </si>
-  <si>
-    <t>FORMULA PG+SK BL STR</t>
-  </si>
-  <si>
-    <t>10017886</t>
-  </si>
-  <si>
-    <t>ORAL B S/G MCKY SOFT</t>
-  </si>
-  <si>
-    <t>20044538</t>
-  </si>
-  <si>
-    <t>HUKI DOT SLC NPL.3/L</t>
-  </si>
-  <si>
-    <t>10019114</t>
-  </si>
-  <si>
-    <t>PIGEON SL.PACIFIER 2</t>
-  </si>
-  <si>
-    <t>20062263</t>
-  </si>
-  <si>
-    <t>PIGEON PRS NPL L 3'S</t>
-  </si>
-  <si>
-    <t>20128874</t>
-  </si>
-  <si>
-    <t>P/A TEAT F/F NRML 2S</t>
-  </si>
-  <si>
-    <t>10011772</t>
-  </si>
-  <si>
-    <t>CUSSONS B/CRM MILD50</t>
-  </si>
-  <si>
-    <t>10033930</t>
-  </si>
-  <si>
-    <t>CUSSON B/CRM SOFT50</t>
-  </si>
-  <si>
-    <t>20133137</t>
-  </si>
-  <si>
-    <t>MY BB FC&amp;BDY CRM 50G</t>
-  </si>
-  <si>
-    <t>20116527</t>
-  </si>
-  <si>
-    <t>ZWITSAL F&amp;B CREAM 50</t>
-  </si>
-  <si>
-    <t>PT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20135794</t>
-  </si>
-  <si>
-    <t>MY BB SOAP SWT.FLO75</t>
-  </si>
-  <si>
-    <t>20099248</t>
-  </si>
-  <si>
-    <t>LCTACYD BB.LIQ SP 60</t>
-  </si>
-  <si>
-    <t>20004868</t>
-  </si>
-  <si>
-    <t>JOHNSON LOTN REG 100</t>
-  </si>
-  <si>
-    <t>20053295</t>
-  </si>
-  <si>
-    <t>JHNSN COLG HPY/B 100</t>
-  </si>
-  <si>
-    <t>20071629</t>
-  </si>
-  <si>
-    <t>JHNSON COLG SLDE 100</t>
-  </si>
-  <si>
-    <t>20013772</t>
-  </si>
-  <si>
-    <t>JOHNSON COLG SUMR100</t>
-  </si>
-  <si>
-    <t>10038388</t>
-  </si>
-  <si>
-    <t>JOHNSON BABY OIL 50M</t>
-  </si>
-  <si>
-    <t>20133138</t>
-  </si>
-  <si>
-    <t>MY BABY BB/OIL PLS90</t>
-  </si>
-  <si>
-    <t>10028608</t>
-  </si>
-  <si>
-    <t>CUSSONS B/OIL SFT100</t>
-  </si>
-  <si>
-    <t>20035884</t>
-  </si>
-  <si>
-    <t>CUSSONS HL.NAT KM100</t>
-  </si>
-  <si>
-    <t>20009870</t>
-  </si>
-  <si>
-    <t>ZWITSAL SHP NAT 100</t>
-  </si>
-  <si>
-    <t>20123404</t>
-  </si>
-  <si>
-    <t>ZWTSAL BB ANBACT 200</t>
   </si>
   <si>
     <t>10033236</t>
@@ -1114,7 +1102,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F105"/>
+  <dimension ref="A1:F103"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1896,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>5</v>
@@ -1907,10 +1895,10 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>100</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
@@ -1919,18 +1907,18 @@
         <v>15</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>101</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>102</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -1939,18 +1927,18 @@
         <v>15</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>104</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
@@ -1959,18 +1947,18 @@
         <v>15</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
@@ -1979,10 +1967,10 @@
         <v>15</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>19</v>
+        <v>106</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -1999,18 +1987,18 @@
         <v>15</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>111</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -2019,18 +2007,18 @@
         <v>15</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>113</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
@@ -2039,18 +2027,18 @@
         <v>15</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>115</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
@@ -2059,18 +2047,18 @@
         <v>15</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>117</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
@@ -2079,18 +2067,18 @@
         <v>15</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>119</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
@@ -2099,10 +2087,10 @@
         <v>15</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -2119,10 +2107,10 @@
         <v>15</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -2139,58 +2127,58 @@
         <v>15</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B52" s="1" t="s">
-        <v>126</v>
-      </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>89</v>
+        <v>4</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>124</v>
+        <v>32</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B53" s="1" t="s">
-        <v>128</v>
-      </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>92</v>
+        <v>8</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>124</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>129</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>130</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
@@ -2199,10 +2187,10 @@
         <v>18</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>32</v>
+        <v>130</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -2219,7 +2207,7 @@
         <v>18</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>19</v>
@@ -2239,18 +2227,18 @@
         <v>18</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>135</v>
+        <v>43</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>137</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
@@ -2259,18 +2247,18 @@
         <v>18</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>138</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>139</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
@@ -2279,7 +2267,7 @@
         <v>18</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>43</v>
@@ -2287,10 +2275,10 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>140</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>141</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
@@ -2299,7 +2287,7 @@
         <v>18</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>43</v>
@@ -2307,10 +2295,10 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>142</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>143</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
@@ -2319,18 +2307,18 @@
         <v>18</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>144</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>145</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
@@ -2339,18 +2327,18 @@
         <v>18</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>43</v>
+        <v>106</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>146</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>147</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
@@ -2359,18 +2347,18 @@
         <v>18</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>32</v>
+        <v>106</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>148</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>149</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
@@ -2379,18 +2367,18 @@
         <v>18</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B64" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>151</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
@@ -2399,58 +2387,58 @@
         <v>18</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B65" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B65" s="1" t="s">
-        <v>153</v>
-      </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>86</v>
+        <v>4</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>109</v>
+        <v>43</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B66" s="1" t="s">
-        <v>155</v>
-      </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>89</v>
+        <v>8</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>109</v>
+        <v>43</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>156</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>157</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
@@ -2459,18 +2447,18 @@
         <v>22</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B68" s="1" t="s">
         <v>158</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>159</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
@@ -2479,10 +2467,10 @@
         <v>22</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>43</v>
+        <v>159</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -2499,7 +2487,7 @@
         <v>22</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>5</v>
@@ -2519,18 +2507,18 @@
         <v>22</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>164</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B71" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>166</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
@@ -2539,7 +2527,7 @@
         <v>22</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>5</v>
@@ -2547,10 +2535,10 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>168</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
@@ -2559,7 +2547,7 @@
         <v>22</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>5</v>
@@ -2567,10 +2555,10 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B73" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>170</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
@@ -2579,7 +2567,7 @@
         <v>22</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>5</v>
@@ -2587,10 +2575,10 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B74" s="1" t="s">
         <v>171</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>172</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
@@ -2599,7 +2587,7 @@
         <v>22</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>5</v>
@@ -2607,10 +2595,10 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>173</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>174</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
@@ -2619,7 +2607,7 @@
         <v>22</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>5</v>
@@ -2627,10 +2615,10 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>175</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>176</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
@@ -2639,7 +2627,7 @@
         <v>22</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>5</v>
@@ -2647,10 +2635,10 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B77" s="1" t="s">
         <v>177</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>178</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
@@ -2659,18 +2647,18 @@
         <v>22</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>179</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>180</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
@@ -2679,18 +2667,18 @@
         <v>22</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>181</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>182</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
@@ -2699,18 +2687,18 @@
         <v>22</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>183</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>184</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
@@ -2719,10 +2707,10 @@
         <v>22</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>92</v>
+        <v>184</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -2739,7 +2727,7 @@
         <v>22</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>95</v>
+        <v>187</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>32</v>
@@ -2747,19 +2735,19 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>32</v>
@@ -2767,30 +2755,30 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>191</v>
+        <v>8</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>32</v>
+        <v>192</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
@@ -2799,7 +2787,7 @@
         <v>25</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>32</v>
@@ -2807,10 +2795,10 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
@@ -2819,10 +2807,10 @@
         <v>25</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>196</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -2839,10 +2827,10 @@
         <v>25</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -2859,7 +2847,7 @@
         <v>25</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>5</v>
@@ -2879,7 +2867,7 @@
         <v>25</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>5</v>
@@ -2899,7 +2887,7 @@
         <v>25</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -2919,10 +2907,10 @@
         <v>25</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -2939,7 +2927,7 @@
         <v>25</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>5</v>
@@ -2959,10 +2947,10 @@
         <v>25</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -2976,10 +2964,10 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -2996,10 +2984,10 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>61</v>
+        <v>12</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3019,7 +3007,7 @@
         <v>28</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3039,10 +3027,10 @@
         <v>28</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3059,10 +3047,10 @@
         <v>28</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3079,7 +3067,7 @@
         <v>28</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>32</v>
@@ -3099,10 +3087,10 @@
         <v>28</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3119,10 +3107,10 @@
         <v>28</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3139,10 +3127,10 @@
         <v>28</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -3159,10 +3147,10 @@
         <v>28</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -3179,49 +3167,9 @@
         <v>28</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A104" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="F104" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A105" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E105" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="F105" s="1" t="s">
         <v>43</v>
       </c>
     </row>

--- a/BKC01D.xlsx
+++ b/BKC01D.xlsx
@@ -1987,7 +1987,7 @@
         <v>15</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>106</v>
@@ -2007,7 +2007,7 @@
         <v>15</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>106</v>
@@ -2027,7 +2027,7 @@
         <v>15</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>106</v>
@@ -2047,7 +2047,7 @@
         <v>15</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>106</v>
@@ -2067,7 +2067,7 @@
         <v>15</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>106</v>
@@ -2087,7 +2087,7 @@
         <v>15</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>119</v>
@@ -2107,7 +2107,7 @@
         <v>15</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>119</v>
@@ -2127,7 +2127,7 @@
         <v>15</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>119</v>
@@ -2967,7 +2967,7 @@
         <v>28</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -2987,7 +2987,7 @@
         <v>28</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3007,7 +3007,7 @@
         <v>28</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3027,7 +3027,7 @@
         <v>28</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>32</v>
@@ -3047,7 +3047,7 @@
         <v>28</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>32</v>
@@ -3067,7 +3067,7 @@
         <v>28</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>32</v>
@@ -3087,7 +3087,7 @@
         <v>28</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3107,7 +3107,7 @@
         <v>28</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3127,7 +3127,7 @@
         <v>28</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>19</v>
@@ -3147,7 +3147,7 @@
         <v>28</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>19</v>
@@ -3167,7 +3167,7 @@
         <v>28</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>43</v>

--- a/BKC01D.xlsx
+++ b/BKC01D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="234">
   <si>
     <t/>
   </si>
@@ -184,12 +184,6 @@
     <t>10</t>
   </si>
   <si>
-    <t>20025364</t>
-  </si>
-  <si>
-    <t>SLEEK P/BTL,DOT 900</t>
-  </si>
-  <si>
     <t>20121430</t>
   </si>
   <si>
@@ -575,6 +569,15 @@
   </si>
   <si>
     <t>17</t>
+  </si>
+  <si>
+    <t>20071630</t>
+  </si>
+  <si>
+    <t>JOHNSON SHP SHNY 100</t>
+  </si>
+  <si>
+    <t>18</t>
   </si>
   <si>
     <t>20005584</t>
@@ -1547,7 +1550,7 @@
         <v>8</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>5</v>
@@ -1555,22 +1558,22 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1587,10 +1590,10 @@
         <v>12</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1607,7 +1610,7 @@
         <v>12</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>5</v>
@@ -1627,7 +1630,7 @@
         <v>12</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>5</v>
@@ -1647,7 +1650,7 @@
         <v>12</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>5</v>
@@ -1667,10 +1670,10 @@
         <v>12</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1687,7 +1690,7 @@
         <v>12</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>19</v>
@@ -1707,7 +1710,7 @@
         <v>12</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>19</v>
@@ -1727,7 +1730,7 @@
         <v>12</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>19</v>
@@ -1747,7 +1750,7 @@
         <v>12</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>19</v>
@@ -1767,10 +1770,10 @@
         <v>12</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1787,7 +1790,7 @@
         <v>12</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>5</v>
@@ -1795,10 +1798,10 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
@@ -1807,7 +1810,7 @@
         <v>12</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>5</v>
@@ -1815,10 +1818,10 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
@@ -1827,7 +1830,7 @@
         <v>12</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>5</v>
@@ -1835,10 +1838,10 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
@@ -1847,7 +1850,7 @@
         <v>12</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>5</v>
@@ -1855,19 +1858,19 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>95</v>
+        <v>4</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>5</v>
@@ -1887,10 +1890,10 @@
         <v>15</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1907,10 +1910,10 @@
         <v>15</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -1927,10 +1930,10 @@
         <v>15</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -1947,18 +1950,18 @@
         <v>15</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>19</v>
+        <v>104</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
@@ -1967,10 +1970,10 @@
         <v>15</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -1987,10 +1990,10 @@
         <v>15</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2007,10 +2010,10 @@
         <v>15</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -2027,10 +2030,10 @@
         <v>15</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -2047,10 +2050,10 @@
         <v>15</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2067,18 +2070,18 @@
         <v>15</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
@@ -2087,10 +2090,10 @@
         <v>15</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -2107,10 +2110,10 @@
         <v>15</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -2124,13 +2127,13 @@
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>89</v>
+        <v>4</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>119</v>
+        <v>32</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -2147,10 +2150,10 @@
         <v>18</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -2167,18 +2170,18 @@
         <v>18</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>19</v>
+        <v>128</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
@@ -2187,10 +2190,10 @@
         <v>18</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>130</v>
+        <v>19</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -2207,10 +2210,10 @@
         <v>18</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -2227,7 +2230,7 @@
         <v>18</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>43</v>
@@ -2247,7 +2250,7 @@
         <v>18</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>43</v>
@@ -2267,7 +2270,7 @@
         <v>18</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>43</v>
@@ -2287,10 +2290,10 @@
         <v>18</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -2307,10 +2310,10 @@
         <v>18</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>32</v>
+        <v>104</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -2327,10 +2330,10 @@
         <v>18</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -2347,10 +2350,10 @@
         <v>18</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -2367,10 +2370,10 @@
         <v>18</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -2384,13 +2387,13 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>89</v>
+        <v>4</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>106</v>
+        <v>43</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -2407,7 +2410,7 @@
         <v>22</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>43</v>
@@ -2427,10 +2430,10 @@
         <v>22</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -2447,18 +2450,18 @@
         <v>22</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>5</v>
+        <v>157</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
@@ -2467,10 +2470,10 @@
         <v>22</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>159</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -2487,7 +2490,7 @@
         <v>22</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>5</v>
@@ -2507,7 +2510,7 @@
         <v>22</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>5</v>
@@ -2527,7 +2530,7 @@
         <v>22</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>5</v>
@@ -2547,7 +2550,7 @@
         <v>22</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>5</v>
@@ -2567,7 +2570,7 @@
         <v>22</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>5</v>
@@ -2587,7 +2590,7 @@
         <v>22</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>5</v>
@@ -2607,7 +2610,7 @@
         <v>22</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>5</v>
@@ -2627,10 +2630,10 @@
         <v>22</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -2647,7 +2650,7 @@
         <v>22</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>43</v>
@@ -2667,10 +2670,10 @@
         <v>22</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -2687,7 +2690,7 @@
         <v>22</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>95</v>
+        <v>182</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>32</v>
@@ -2695,10 +2698,10 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
@@ -2707,7 +2710,7 @@
         <v>22</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>32</v>
@@ -2715,10 +2718,10 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
@@ -2727,18 +2730,18 @@
         <v>22</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
@@ -2755,10 +2758,10 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
@@ -2770,15 +2773,15 @@
         <v>8</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
@@ -2795,10 +2798,10 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
@@ -2815,10 +2818,10 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
@@ -2835,10 +2838,10 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
@@ -2855,10 +2858,10 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
@@ -2875,10 +2878,10 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
@@ -2895,10 +2898,10 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
@@ -2915,10 +2918,10 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
@@ -2935,10 +2938,10 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
@@ -2947,7 +2950,7 @@
         <v>25</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -2955,10 +2958,10 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
@@ -2975,10 +2978,10 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
@@ -2995,10 +2998,10 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
@@ -3015,10 +3018,10 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
@@ -3035,10 +3038,10 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
@@ -3055,10 +3058,10 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
@@ -3075,10 +3078,10 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
@@ -3095,10 +3098,10 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
@@ -3115,10 +3118,10 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
@@ -3135,10 +3138,10 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
@@ -3155,10 +3158,10 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
@@ -3167,7 +3170,7 @@
         <v>28</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>43</v>

--- a/BKC01D.xlsx
+++ b/BKC01D.xlsx
@@ -475,7 +475,7 @@
     <t>20133137</t>
   </si>
   <si>
-    <t>MY BB FC&amp;BDY CRM 50G</t>
+    <t>MY BB FC&amp;BDY NOURI50</t>
   </si>
   <si>
     <t>20116527</t>

--- a/BKC01D.xlsx
+++ b/BKC01D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="251">
   <si>
     <t/>
   </si>
@@ -241,52 +241,100 @@
     <t>KDOMO B.WASH STR 200</t>
   </si>
   <si>
+    <t>20113805</t>
+  </si>
+  <si>
+    <t>KDOMO B.WASH ORG 200</t>
+  </si>
+  <si>
+    <t>20143473</t>
+  </si>
+  <si>
+    <t>B&amp;B S&amp;C GLY SH200+50</t>
+  </si>
+  <si>
+    <t>20143316</t>
+  </si>
+  <si>
+    <t>ZWTSL B/B ANTIBAC300</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20012094</t>
+  </si>
+  <si>
+    <t>ZWITSAL B/BATH MH300</t>
+  </si>
+  <si>
+    <t>20143472</t>
+  </si>
+  <si>
+    <t>BB HAIR&amp;BW PMP240+60</t>
+  </si>
+  <si>
+    <t>20135607</t>
+  </si>
+  <si>
+    <t>MB KIDS HBC LVELY100</t>
+  </si>
+  <si>
+    <t>20113917</t>
+  </si>
+  <si>
+    <t>MB KIDS HBC SWT 100</t>
+  </si>
+  <si>
+    <t>20113918</t>
+  </si>
+  <si>
+    <t>MB KIDS HBC FRSH100</t>
+  </si>
+  <si>
+    <t>20143470</t>
+  </si>
+  <si>
+    <t>B&amp;B SPRAY CLGNE80+20</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>20143330</t>
+  </si>
+  <si>
+    <t>B&amp;B HAIR LT SPRY100</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>20090401</t>
+  </si>
+  <si>
+    <t>KDOMO SH&amp;CON BLU 200</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
     <t>20134006</t>
   </si>
   <si>
     <t>KDOMO SH&amp;CON CHRY200</t>
   </si>
   <si>
-    <t>20090401</t>
-  </si>
-  <si>
-    <t>KDOMO SH&amp;CON BLU 200</t>
-  </si>
-  <si>
-    <t>20113805</t>
-  </si>
-  <si>
-    <t>KDOMO B.WASH ORG 200</t>
-  </si>
-  <si>
-    <t>20143473</t>
-  </si>
-  <si>
-    <t>B&amp;B S&amp;C GLY SH200+50</t>
-  </si>
-  <si>
-    <t>20143472</t>
-  </si>
-  <si>
-    <t>BB HAIR&amp;BW PMP240+60</t>
-  </si>
-  <si>
-    <t>20135607</t>
-  </si>
-  <si>
-    <t>MB KIDS HBC LVELY100</t>
-  </si>
-  <si>
-    <t>20113917</t>
-  </si>
-  <si>
-    <t>MB KIDS HBC SWT 100</t>
-  </si>
-  <si>
-    <t>20113918</t>
-  </si>
-  <si>
-    <t>MB KIDS HBC FRSH100</t>
+    <t>17</t>
+  </si>
+  <si>
+    <t>20130478</t>
+  </si>
+  <si>
+    <t>DOREMI COLG GLACR100</t>
+  </si>
+  <si>
+    <t>18</t>
   </si>
   <si>
     <t>20008706</t>
@@ -295,25 +343,7 @@
     <t>MASTER CLG SPRMN 100</t>
   </si>
   <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>20130478</t>
-  </si>
-  <si>
-    <t>DOREMI COLG GLACR100</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>20143470</t>
-  </si>
-  <si>
-    <t>B&amp;B SPRAY CLGNE80+20</t>
-  </si>
-  <si>
-    <t>16</t>
+    <t>19</t>
   </si>
   <si>
     <t>20135794</t>
@@ -598,9 +628,6 @@
     <t>CUSSONS B/CRM MILD50</t>
   </si>
   <si>
-    <t>17</t>
-  </si>
-  <si>
     <t>20005584</t>
   </si>
   <si>
@@ -611,9 +638,6 @@
   </si>
   <si>
     <t>ZWTSAL B.BATH R.H400</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
   </si>
   <si>
     <t>20110812</t>
@@ -1132,7 +1156,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F108"/>
+  <dimension ref="A1:F111"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1760,7 +1784,7 @@
         <v>26</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1780,15 +1804,15 @@
         <v>29</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>23</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
@@ -1800,15 +1824,15 @@
         <v>32</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
@@ -1825,10 +1849,10 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
@@ -1845,10 +1869,10 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
@@ -1865,10 +1889,10 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
@@ -1885,10 +1909,10 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
@@ -1897,18 +1921,18 @@
         <v>12</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
@@ -1917,18 +1941,18 @@
         <v>12</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
@@ -1937,7 +1961,7 @@
         <v>12</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>23</v>
@@ -1945,39 +1969,39 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>4</v>
+        <v>104</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>8</v>
+        <v>107</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>9</v>
@@ -1985,19 +2009,19 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>12</v>
+        <v>110</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>9</v>
@@ -2005,10 +2029,10 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
@@ -2017,18 +2041,18 @@
         <v>15</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>109</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -2037,18 +2061,18 @@
         <v>15</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>109</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
@@ -2057,18 +2081,18 @@
         <v>15</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>109</v>
+        <v>9</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
@@ -2077,18 +2101,18 @@
         <v>15</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>23</v>
+        <v>119</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
@@ -2097,18 +2121,18 @@
         <v>15</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>38</v>
+        <v>119</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
@@ -2117,18 +2141,18 @@
         <v>15</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>23</v>
+        <v>119</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
@@ -2137,18 +2161,18 @@
         <v>15</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>122</v>
+        <v>23</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
@@ -2157,18 +2181,18 @@
         <v>15</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>122</v>
+        <v>38</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
@@ -2177,18 +2201,18 @@
         <v>15</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>122</v>
+        <v>23</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
@@ -2197,18 +2221,18 @@
         <v>15</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
@@ -2217,18 +2241,18 @@
         <v>15</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
@@ -2237,78 +2261,78 @@
         <v>15</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>4</v>
+        <v>65</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>38</v>
+        <v>132</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>23</v>
+        <v>132</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>12</v>
+        <v>98</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
@@ -2317,18 +2341,18 @@
         <v>18</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
@@ -2337,18 +2361,18 @@
         <v>18</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
@@ -2357,18 +2381,18 @@
         <v>18</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>5</v>
+        <v>149</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
@@ -2377,18 +2401,18 @@
         <v>18</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
@@ -2397,18 +2421,18 @@
         <v>18</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>38</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
@@ -2417,18 +2441,18 @@
         <v>18</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>122</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
@@ -2437,18 +2461,18 @@
         <v>18</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>122</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
@@ -2457,18 +2481,18 @@
         <v>18</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>122</v>
+        <v>38</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
@@ -2477,18 +2501,18 @@
         <v>18</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
@@ -2497,78 +2521,78 @@
         <v>18</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>5</v>
+        <v>132</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>4</v>
+        <v>59</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>5</v>
+        <v>132</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>164</v>
+        <v>132</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
@@ -2577,18 +2601,18 @@
         <v>22</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
@@ -2597,18 +2621,18 @@
         <v>22</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>9</v>
+        <v>174</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
@@ -2617,7 +2641,7 @@
         <v>22</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>9</v>
@@ -2625,10 +2649,10 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
@@ -2637,7 +2661,7 @@
         <v>22</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>9</v>
@@ -2645,10 +2669,10 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
@@ -2657,7 +2681,7 @@
         <v>22</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>9</v>
@@ -2665,10 +2689,10 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
@@ -2677,7 +2701,7 @@
         <v>22</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>9</v>
@@ -2685,10 +2709,10 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
@@ -2697,18 +2721,18 @@
         <v>22</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
@@ -2717,18 +2741,18 @@
         <v>22</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
@@ -2737,7 +2761,7 @@
         <v>22</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>9</v>
@@ -2745,10 +2769,10 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
@@ -2757,18 +2781,18 @@
         <v>22</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
@@ -2777,18 +2801,18 @@
         <v>22</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>38</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
@@ -2797,18 +2821,18 @@
         <v>22</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
@@ -2817,18 +2841,18 @@
         <v>22</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
@@ -2837,27 +2861,27 @@
         <v>22</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>195</v>
+        <v>95</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>38</v>
@@ -2865,50 +2889,50 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>8</v>
+        <v>101</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>200</v>
+        <v>38</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>12</v>
+        <v>104</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>38</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
@@ -2917,18 +2941,18 @@
         <v>26</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
@@ -2937,18 +2961,18 @@
         <v>26</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
@@ -2957,18 +2981,18 @@
         <v>26</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
@@ -2977,7 +3001,7 @@
         <v>26</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>9</v>
@@ -2985,10 +3009,10 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
@@ -2997,7 +3021,7 @@
         <v>26</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>9</v>
@@ -3005,10 +3029,10 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
@@ -3017,18 +3041,18 @@
         <v>26</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
@@ -3037,7 +3061,7 @@
         <v>26</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>9</v>
@@ -3045,10 +3069,10 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
@@ -3057,7 +3081,7 @@
         <v>26</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>9</v>
@@ -3065,39 +3089,39 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>9</v>
@@ -3105,19 +3129,19 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>9</v>
@@ -3125,10 +3149,10 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
@@ -3137,18 +3161,18 @@
         <v>29</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
@@ -3157,18 +3181,18 @@
         <v>29</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
@@ -3177,18 +3201,18 @@
         <v>29</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
@@ -3197,7 +3221,7 @@
         <v>29</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>38</v>
@@ -3205,10 +3229,10 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
@@ -3217,18 +3241,18 @@
         <v>29</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
@@ -3237,18 +3261,18 @@
         <v>29</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
@@ -3257,18 +3281,18 @@
         <v>29</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
@@ -3277,18 +3301,18 @@
         <v>29</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
@@ -3297,9 +3321,69 @@
         <v>29</v>
       </c>
       <c r="E108" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E111" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F108" s="1" t="s">
+      <c r="F111" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/BKC01D.xlsx
+++ b/BKC01D.xlsx
@@ -145,13 +145,13 @@
     <t>20001546</t>
   </si>
   <si>
-    <t>MITU TIS.G/P BLU2X50</t>
+    <t>MITU G/P BLUE 2x50'S</t>
   </si>
   <si>
     <t>20071105</t>
   </si>
   <si>
-    <t>MITU GP PURPLE 2X50S</t>
+    <t>MITU TIS. PF 2x50'S</t>
   </si>
   <si>
     <t>20087203</t>
@@ -181,13 +181,13 @@
     <t>20035113</t>
   </si>
   <si>
-    <t>MITU WIPE BLUE BB 40</t>
+    <t>MITU WIPE BB 2x40'S</t>
   </si>
   <si>
     <t>20001061</t>
   </si>
   <si>
-    <t>MITU G/P PINK 2X50'S</t>
+    <t>MITU G/P PINK 2x50'S</t>
   </si>
   <si>
     <t>11</t>
